--- a/Hyper_Parameters.xlsx
+++ b/Hyper_Parameters.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajal\AI Course\ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajal\AI Course\ML\3.SVMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBE3427-E4D7-4DCF-B32D-9A05C35B7A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4669A5A-DF56-458A-B7B8-E237303397DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{03B7BF59-44C5-408E-B748-4FCD87A2AE4E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{03B7BF59-44C5-408E-B748-4FCD87A2AE4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Decision Tree" sheetId="1" r:id="rId1"/>
+    <sheet name="Supporting Vectorkernel" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>criterion</t>
   </si>
@@ -61,13 +62,40 @@
   </si>
   <si>
     <t>random</t>
+  </si>
+  <si>
+    <t>kernel</t>
+  </si>
+  <si>
+    <t>R2_score</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>poly</t>
+  </si>
+  <si>
+    <t>rbf</t>
+  </si>
+  <si>
+    <t>sigmoid</t>
+  </si>
+  <si>
+    <t>precomputed</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>NA - Applicable only for Square matrix</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,8 +131,37 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF222832"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF222832"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,6 +171,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -130,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -140,6 +203,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -567,4 +642,146 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F84014-00BD-402D-9BC4-594A6D7C1392}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0.92399834281181104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8">
+        <v>10000</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.81296283670202296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8">
+        <v>10000</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.37189506360095498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8">
+        <v>10000</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.85353111963688599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="8">
+        <v>10000</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11">
+        <v>20000</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.93012474942329904</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="8">
+        <v>20000</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.67169369276385904</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="8">
+        <v>20000</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.53324426083917797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="8">
+        <v>20000</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.90111528577578903</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8">
+        <v>30000</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.81438220618977297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.35">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>